--- a/TESTS/zlit_6_baiky.xlsx
+++ b/TESTS/zlit_6_baiky.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -603,6 +608,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Короткий алегоричний твір (частіше про тварин) що містить повчальний висновок — мораль</t>
+          <t>Короткий алегоричний твір (частіше про тварин) що містить повчальний висновок</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Обов'язкова мораль — чіткий повчальний висновок який формулює автор або випливає з дії</t>
+          <t>Обов'язкова мораль</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Хто не може отримати бажане — починає зневажати те чого прагнув: «зелений виноград»</t>
+          <t>Хто не може отримати бажане</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Не змогла дістати і виправдала своє безсилля — це психологічний захист що дістав назву «кисле виноград»</t>
+          <t>Не змогла дістати і виправдала своє безсилля</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Самовиправдання і зневагу до того чого не можеш досягти — замість визнати поразку людина знецінює мету</t>
+          <t>Самовиправдання і зневагу до того чого не можеш досягти</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Сила завжди знайде привід — тиран не потребує справжнього приводу аби скривдити слабкого</t>
+          <t>Сила завжди знайде привід</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Вигадує одне за одним безглузді звинувачення на адресу Ягняти — усвідомлюючи що хоче з'їсти незалежно від правди</t>
+          <t>Вигадує одне за одним безглузді звинувачення на адресу Ягняти</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Вовк — тирана і того хто має владу; Ягня — беззахисного і правого але слабкого</t>
+          <t>Вовк</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Чим займалась Мурашка влітку, за байкою «Мурашка і Цикада»?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Співала і танцювала</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Старанно запасала їжу на зиму</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спала цілий день</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Будувала будинок</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що робила Цикада (Стрибунець) ціле літо?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Працювала разом з Мурашкою</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Співала і веселилась, не думаючи про майбутнє</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спала</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Збирала зерно</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що сталося з Цикадою, коли настала зима?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона знайшла власні запаси</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Голодна, вона прийшла просити їжі у Мурашки, яка відмовила</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона полетіла на південь</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сталось</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Що тримала у дзьобі Ворона, коли її побачила Лисиця?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гілку</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шматок сиру</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ягоду</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Камінець</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Якими словами Лисиця хитро підлестилась до Ворони?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вимагала віддати сир</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Похвалила її красу і голос, попросивши заспівати</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Запропонувала обмін</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Погрозила їй</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що сталося, коли Ворона розкрила дзьоб, щоб заспівати?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не сталось</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сир упав, і Лисиця його схопила</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ворона заспівала гарно</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лисиця втекла</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Що робив хлопчик-пастушок заради розваги?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Грав на сопілці</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кілька разів даремно кричав «Вовк!», щоб подивитись, як люди прибіжать</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Малював вовків</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дражнив овець</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як реагували люди на крики хлопчика спочатку?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не звертали уваги</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Прибігали на допомогу, але виявляли, що вовка немає</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сміялися з нього одразу</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Карали його одразу</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що сталося, коли вовк справді прийшов?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Люди одразу прибігли</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ніхто не повірив хлопчику, і вовк завдав шкоди отарі</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Хлопчик сам прогнав вовка</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не сталось</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що зробив Лев, коли прокинувся і побачив Мишу, що пробігла по ньому?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розгнівано вбив її одразу</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спершу хотів покарати, але відпустив, коли Миша пообіцяла стати в нагоді</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не помітив її</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Засміявся і відпустив без слів</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як Миша допомогла Леву пізніше?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Принесла йому їжу</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Прогризла мисливську сітку, в яку потрапив Лев, і звільнила його</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Покликала інших тварин на допомогу</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Налякала мисливців</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Яка мораль байки «Лев і Миша»?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сильні завжди перемагають</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Навіть найменший і слабший може стати в нагоді найсильнішому</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Тварини не допомагають одна одній</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Леви небезпечні</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Чому Заєць погодився побігти на змагання з Черепахою?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Йому наказали</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він був упевнений у легкій перемозі і кепкував з повільної Черепахи</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він боявся Черепахи</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Йому пообіцяли нагороду</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що зробив Заєць посеред перегонів, опинившись попереду?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Продовжив біг</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Самовпевнено заснув, вважаючи, що встигне</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Збився з дороги</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Здався і пішов додому</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Хто переміг у перегонах Зайця і Черепахи і чому?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заєць, бо він швидший</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Черепаха, бо повільно, але неухильно рухалась до фінішу, поки Заєць спав</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нічия</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Жоден не дійшов до фінішу</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>З яких двох частин зазвичай складається байка?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вступу і висновку</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Оповідної частини (історії) та моралі (повчального висновку)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Опису і діалогу</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Питання і відповіді</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому персонажами байок найчастіше є тварини, а не люди?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так простіше малювати</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Через образи тварин зручно й безпечно показувати людські риси та вади</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо тварини справді так розмовляють</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Так наказували правителі</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Де в байці найчастіше міститься мораль?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише на початку</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найчастіше в кінці, хоча іноді трапляється і на початку</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Завжди в середині</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Моралі в байках не буває</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що означає вислів «езопова мова»?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Давньогрецька мова</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спосіб говорити про серйозні речі натяками та алегоріями, уникаючи прямої критики</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Мова тварин у казках</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Стародавня писемність</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому байки Езопа залишаються актуальними тисячоліттями?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони дуже довгі</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Людські вади, які вони висміюють, не зникають з часом</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їх легко перекладати</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони про тварин</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що зробив Лафонтен із сюжетами Езопа?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Просто переклав їх</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Переробив у витончені віршовані байки французькою мовою, надавши нової художньої форми</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Заборонив їх</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Переписав про людей замість тварин</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що таке «алегорія» у байці?</t>
+          <t>Алегорія — це спосіб зображення абстрактних понять чи якостей через конкретні образи, наприклад тварин.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що таке «езопова мова» як культурний вираз?</t>
+          <t>«Езопова мова» — це назва стародавньої грецької абетки.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому байки зберігають актуальність тисячоліттями?</t>
+          <t>Байки залишаються актуальними, бо людські вади, які вони висміюють, існують у будь-яку епоху.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Якого Осла засудили у байці Лафонтена і чому це несправедливо?</t>
+          <t>У байці Лафонтена «Зачумлені звірі» покарали саме Осла, хоча найбільші «грішники» — могутні тварини — уникли відповідальності.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка мораль байки «Зачумлені звірі» Лафонтена?</t>
+          <t>Мораль «Зачумлених звірів» — сильні часто звинувачують слабших, уникаючи відповідальності самі.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між байками Езопа і Лафонтена?</t>
+          <t>Байки Езопа і Лафонтена не мають нічого спільного, окрім того, що в обох діють тварини.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які ознаки притаманні жанру байки?</t>
+          <t>Які тварини є персонажами розглянутих байок?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Алегоричні образи (зазвичай тварини)</t>
+          <t>Лисиця</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Обов'язкова мораль</t>
+          <t>Вовк</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Великий обсяг</t>
+          <t>Дракон</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Повчальний зміст</t>
+          <t>Ягня</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Відповідальність у суспільстві — сильні звірі перекладають провину на слабкого Осла що вчинив найменший гріх</t>
+          <t>Відповідальність у суспільстві</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Звірі збираються щоб визначити хто грішніший і принести жертву — сильні виправдовуються а безвинного Осла засуджують</t>
+          <t>Звірі збираються щоб визначити хто грішніший і принести жертву</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
